--- a/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
+++ b/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sirh\assets\Formato\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin.hernandez\Desktop\REGISTROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17CB908-ED81-4B9F-89AC-59916EC3EC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A57CFEC0-EFD8-4153-B452-C46168980BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDFFC4D4-785C-409B-827D-72446BEA2B34}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>RFC*</t>
   </si>
   <si>
-    <t>FECHA (YYYY/MM/DD) *</t>
-  </si>
-  <si>
     <t>OBSERVACIONES</t>
   </si>
   <si>
@@ -51,6 +48,9 @@
   </si>
   <si>
     <t>TIPO DE FALTA/RETARDO</t>
+  </si>
+  <si>
+    <t>FECHA (YYYY-MM-DD) *</t>
   </si>
 </sst>
 </file>
@@ -467,16 +467,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">

--- a/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
+++ b/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin.hernandez\Desktop\REGISTROS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin.hernandez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A57CFEC0-EFD8-4153-B452-C46168980BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D31650F-0553-4FC4-9022-8ADE5E873C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDFFC4D4-785C-409B-827D-72446BEA2B34}"/>
   </bookViews>
@@ -47,10 +47,10 @@
     <t>TIPO</t>
   </si>
   <si>
-    <t>TIPO DE FALTA/RETARDO</t>
+    <t>FECHA (YYYY-MM-DD) *</t>
   </si>
   <si>
-    <t>FECHA (YYYY-MM-DD) *</t>
+    <t>PERIODO VACACIONAL</t>
   </si>
 </sst>
 </file>
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">

--- a/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
+++ b/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin.hernandez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D31650F-0553-4FC4-9022-8ADE5E873C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32671DBF-5C46-42C1-AB13-613BF0056532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDFFC4D4-785C-409B-827D-72446BEA2B34}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$14349</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,16 +50,19 @@
     <t>TIPO</t>
   </si>
   <si>
-    <t>FECHA (YYYY-MM-DD) *</t>
+    <t>TIPO DE FALTA/RETARDO</t>
   </si>
   <si>
-    <t>PERIODO VACACIONAL</t>
+    <t>FECHA (YYYY-MM-DD) *</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -80,12 +86,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -111,18 +114,44 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 8" xfId="1" xr:uid="{05FCA60A-551C-4063-9B2F-407A12FD84CA}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -452,14 +481,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33197F3C-A688-4A19-9EEC-36F4DBAF7D57}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G5056"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="40.5703125" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -467,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -476,14 +506,50 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="2"/>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F41" s="3"/>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G84" s="3"/>
+    </row>
+    <row r="167" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F167" s="3"/>
+    </row>
+    <row r="168" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F168" s="3"/>
+    </row>
+    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C252" s="3"/>
+    </row>
+    <row r="259" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G259" s="3"/>
+    </row>
+    <row r="1002" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1002" s="3"/>
+    </row>
+    <row r="5056" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C5056" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G1:G5906 G14350:G1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
+++ b/assets/Formato/LAYOUT_JUSTIFICACION.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin.hernandez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32671DBF-5C46-42C1-AB13-613BF0056532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D31650F-0553-4FC4-9022-8ADE5E873C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDFFC4D4-785C-409B-827D-72446BEA2B34}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$14349</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -50,19 +47,16 @@
     <t>TIPO</t>
   </si>
   <si>
-    <t>TIPO DE FALTA/RETARDO</t>
+    <t>FECHA (YYYY-MM-DD) *</t>
   </si>
   <si>
-    <t>FECHA (YYYY-MM-DD) *</t>
+    <t>PERIODO VACACIONAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -86,9 +80,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -114,44 +111,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 8" xfId="1" xr:uid="{05FCA60A-551C-4063-9B2F-407A12FD84CA}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -481,15 +452,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33197F3C-A688-4A19-9EEC-36F4DBAF7D57}">
-  <dimension ref="A1:G5056"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="40.5703125" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -497,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -506,50 +476,14 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F41" s="3"/>
-    </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G84" s="3"/>
-    </row>
-    <row r="167" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F167" s="3"/>
-    </row>
-    <row r="168" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F168" s="3"/>
-    </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C252" s="3"/>
-    </row>
-    <row r="259" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G259" s="3"/>
-    </row>
-    <row r="1002" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1002" s="3"/>
-    </row>
-    <row r="5056" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5056" s="3"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G1:G5906 G14350:G1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>